--- a/2.Hardware/1.PCB/4.ServoShield/6.BOM/BOMSheild.xlsx
+++ b/2.Hardware/1.PCB/4.ServoShield/6.BOM/BOMSheild.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="65">
   <si>
     <t>Name</t>
   </si>
@@ -59,6 +59,9 @@
     <t>C1</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/tu-gom-0805-100nf-0-1uf-50v</t>
+  </si>
+  <si>
     <t>SMAJ18A</t>
   </si>
   <si>
@@ -68,12 +71,21 @@
     <t>D1, D3</t>
   </si>
   <si>
-    <t>Schottky-Diode</t>
+    <t>https://www.thegioiic.com/smaj18a</t>
+  </si>
+  <si>
+    <t>ZMM18</t>
+  </si>
+  <si>
+    <t>18V Zener diode</t>
   </si>
   <si>
     <t>D2, D4</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/zmm18-diode-zener-18v-500mw-smd</t>
+  </si>
+  <si>
     <t>160603RedBlur</t>
   </si>
   <si>
@@ -83,6 +95,9 @@
     <t>D5</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/led-do-0603-dan-smd-trong-suot</t>
+  </si>
+  <si>
     <t>0605201000250</t>
   </si>
   <si>
@@ -92,6 +107,9 @@
     <t>F1</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/cau-chi-ong-thuy-tinh-30a-5x20mm-toc-do-f</t>
+  </si>
+  <si>
     <t>KF301-2P</t>
   </si>
   <si>
@@ -101,30 +119,45 @@
     <t>J1</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb</t>
+  </si>
+  <si>
     <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 24p</t>
   </si>
   <si>
     <t>J2, J3, J5</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-24-chan-2-hang-smd</t>
+  </si>
+  <si>
     <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 8p</t>
   </si>
   <si>
     <t>J4, J7</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-8-chan-2-hang-smd</t>
+  </si>
+  <si>
     <t>WR-PHD Socket Header, SMT, pitch 2.54mm, Dual Row, Vertical, 20p</t>
   </si>
   <si>
     <t>J6</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-20-chan-2-hang-smd</t>
+  </si>
+  <si>
     <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 24p</t>
   </si>
   <si>
     <t>P1, P2, P3</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd</t>
+  </si>
+  <si>
     <t>WR-PHD Pin Header, SMT, pitch 2.54mm, Dual Row, Vertical, 20p</t>
   </si>
   <si>
@@ -137,6 +170,9 @@
     <t>P5, P6, P7, P8, P9, P10, P11, P12, P13, P14, P15, P16, P17, P18, P19, P20</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/hang-rao-duc-don-2-54mm-40-chan-1-hang-cao-11-2mm-xuyen-lo</t>
+  </si>
+  <si>
     <t>AOD4185</t>
   </si>
   <si>
@@ -146,6 +182,9 @@
     <t>Q1, Q2, Q3</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/ao3407a-mosfet-kenh-p-30v-4-3a-sot-23-3</t>
+  </si>
+  <si>
     <t>0008051531</t>
   </si>
   <si>
@@ -155,6 +194,9 @@
     <t>R1, R2, R3</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/dien-tro-15-kohm-0805-5-</t>
+  </si>
+  <si>
     <t>0006031021</t>
   </si>
   <si>
@@ -164,24 +206,46 @@
     <t>R4</t>
   </si>
   <si>
+    <t>https://www.thegioiic.com/dien-tro-1-kohm-0603-5-</t>
+  </si>
+  <si>
     <t>MP3.2</t>
   </si>
   <si>
     <t>Scr1, Scr2, Scr3, Scr4</t>
+  </si>
+  <si>
+    <t>https://www.thegioiic.com/vit-nhua-m3-dai-5mm</t>
+  </si>
+  <si>
+    <t>PCB</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="6">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ [$VND]\ * #,##0.00_ ;_ [$VND]\ * \-#,##0.00_ ;_ [$VND]\ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="[$VND]\ #,##0.00;[$VND]\ \-#,##0.00"/>
   </numFmts>
-  <fonts count="20">
-    <font>
+  <fonts count="22">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -202,6 +266,14 @@
       <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -653,138 +725,159 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
@@ -1323,41 +1416,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="15.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="70.8888888888889" customWidth="1"/>
     <col min="3" max="3" width="64" customWidth="1"/>
     <col min="4" max="4" width="18.4444444444444" customWidth="1"/>
-    <col min="6" max="6" width="10.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="14.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="15.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
@@ -1367,214 +1461,422 @@
         <v>9</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>190</v>
+      </c>
+      <c r="F2" s="3">
+        <f t="shared" ref="F2:F18" si="0">E2*D2</f>
+        <v>190</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
+      <c r="E3" s="2">
+        <v>500</v>
+      </c>
+      <c r="F3" s="3">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>200</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
+      <c r="E5" s="2">
+        <v>180</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="0"/>
+        <v>180</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
+    <row r="6" spans="1:7">
+      <c r="A6" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>500</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
+      <c r="E7" s="2">
+        <v>1500</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:7">
       <c r="A8">
         <v>61032421821</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>4200</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="0"/>
+        <v>12600</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:7">
       <c r="A9">
         <v>61030821821</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1500</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="0"/>
+        <v>3000</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:7">
       <c r="A10">
         <v>61032021821</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>3700</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="0"/>
+        <v>3700</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:7">
       <c r="A11">
         <v>61002421121</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4500</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="0"/>
+        <v>13500</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:7">
       <c r="A12">
         <v>61032021121</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D12">
         <v>1</v>
       </c>
+      <c r="E12" s="2">
+        <v>4500</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="0"/>
+        <v>4500</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:7">
       <c r="A13">
         <v>61300311121</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>16</v>
+      </c>
+      <c r="E13" s="2">
+        <v>700</v>
+      </c>
+      <c r="F13" s="3">
+        <f t="shared" si="0"/>
+        <v>11200</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
+      <c r="E14" s="2">
+        <v>2000</v>
+      </c>
+      <c r="F14" s="3">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>39</v>
+    <row r="15" spans="1:7">
+      <c r="A15" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="D15">
         <v>3</v>
       </c>
+      <c r="E15" s="2">
+        <v>50</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" si="0"/>
+        <v>150</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>55</v>
+      </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>42</v>
+    <row r="16" spans="1:7">
+      <c r="A16" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D16">
         <v>1</v>
       </c>
+      <c r="E16" s="2">
+        <v>32</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="E17" s="2">
+        <v>380</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="0"/>
+        <v>1520</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3">
+        <v>20000</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="19" spans="5:6">
+      <c r="E19" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F19" s="7">
+        <f>SUM(F2:F18)-4*E18</f>
+        <v>79972</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.thegioiic.com/tu-gom-0805-100nf-0-1uf-50v"/>
+    <hyperlink ref="G3" r:id="rId2" display="https://www.thegioiic.com/smaj18a"/>
+    <hyperlink ref="G4" r:id="rId3" display="https://www.thegioiic.com/zmm18-diode-zener-18v-500mw-smd"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://www.thegioiic.com/led-do-0603-dan-smd-trong-suot"/>
+    <hyperlink ref="G6" r:id="rId5" display="https://www.thegioiic.com/cau-chi-ong-thuy-tinh-30a-5x20mm-toc-do-f"/>
+    <hyperlink ref="G7" r:id="rId6" display="https://www.thegioiic.com/kf301-2-v-domino-2-chan-thang-5-08mm-300v-10a-han-pcb"/>
+    <hyperlink ref="G11" r:id="rId7" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd"/>
+    <hyperlink ref="G12" r:id="rId7" display="https://www.thegioiic.com/hang-rao-duc-doi-2-54mm-80-chan-2-hang-smd"/>
+    <hyperlink ref="G13" r:id="rId8" display="https://www.thegioiic.com/hang-rao-duc-don-2-54mm-40-chan-1-hang-cao-11-2mm-xuyen-lo"/>
+    <hyperlink ref="G8" r:id="rId9" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-24-chan-2-hang-smd"/>
+    <hyperlink ref="G10" r:id="rId10" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-20-chan-2-hang-smd"/>
+    <hyperlink ref="G9" r:id="rId11" display="https://www.thegioiic.com/hang-rao-cai-doi-2-54mm-8-chan-2-hang-smd"/>
+    <hyperlink ref="G14" r:id="rId12" display="https://www.thegioiic.com/ao3407a-mosfet-kenh-p-30v-4-3a-sot-23-3"/>
+    <hyperlink ref="G15" r:id="rId13" display="https://www.thegioiic.com/dien-tro-15-kohm-0805-5-"/>
+    <hyperlink ref="G16" r:id="rId14" display="https://www.thegioiic.com/dien-tro-1-kohm-0603-5-"/>
+    <hyperlink ref="G17" r:id="rId15" display="https://www.thegioiic.com/vit-nhua-m3-dai-5mm"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
